--- a/UPMPackages/com.solotopia.nova.framework.kit.network.gamelogin/Nova/Tracks/Tracks.xlsx
+++ b/UPMPackages/com.solotopia.nova.framework.kit.network.gamelogin/Nova/Tracks/Tracks.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -194,8 +194,21 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体-简"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="38">
+  <fills count="39">
     <fill>
       <patternFill/>
     </fill>
@@ -415,8 +428,14 @@
         <fgColor rgb="FFFFF4D8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -570,6 +589,15 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9E2F3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -718,7 +746,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -759,6 +787,16 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1172,357 +1210,353 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
-    <col width="35" customWidth="1" style="1" min="1" max="1"/>
-    <col width="31" customWidth="1" style="1" min="2" max="2"/>
-    <col width="55" customWidth="1" style="1" min="3" max="3"/>
+    <col width="28" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="36" customWidth="1" style="1" min="3" max="3"/>
     <col width="40" customWidth="1" style="1" min="4" max="4"/>
-    <col width="13" customWidth="1" style="1" min="5" max="5"/>
-    <col width="55" customWidth="1" style="1" min="6" max="7"/>
-    <col width="11" customWidth="1" style="1" min="8" max="8"/>
-    <col width="55" customWidth="1" style="1" min="9" max="9"/>
+    <col width="14" customWidth="1" style="1" min="5" max="5"/>
+    <col width="58" customWidth="1" style="1" min="6" max="6"/>
+    <col width="32" customWidth="1" style="1" min="7" max="7"/>
+    <col width="16" customWidth="1" style="1" min="8" max="8"/>
+    <col width="48" customWidth="1" style="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" s="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="18" t="inlineStr">
         <is>
           <t>事件名</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t>事件中文名</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="18" t="inlineStr">
         <is>
           <t>事件说明</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="18" t="inlineStr">
         <is>
           <t>属性名</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>属性类型</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>属性说明</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>上报时机</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1" s="1">
-      <c r="A2" s="10" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>nova_gamelogin_login</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>登录完成</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>GameLogin 登录请求完成。成功、失败或异常均只上报一次。</t>
         </is>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_login_type</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="21" t="inlineStr">
         <is>
           <t>登录方式。uid=UID 登录；third_party=第三方 OpenID 登录；force_new=强制注册新账号。</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="21" t="inlineStr">
         <is>
           <t>Login.Async 请求取得最终结果时上报。</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I2" s="10" t="inlineStr">
-        <is>
-          <t>成功时先关联响应 UID；OpenID 非空时更新用户属性 nova_openid，再上报本事件。</t>
+      <c r="I2" s="21" t="inlineStr">
+        <is>
+          <t>成功时主登录链关联响应 UID；响应 Data.Openid 非空时更新用户属性 nova_openid，再上报本事件。</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="14.5" customHeight="1" s="1">
+    <row r="3">
       <c r="A3" s="12" t="n"/>
       <c r="B3" s="12" t="n"/>
       <c r="C3" s="12" t="n"/>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_login_result</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>登录结果。success=成功；failed=请求失败；exception=调用抛出异常。</t>
         </is>
       </c>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="12" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="G3" s="21" t="n"/>
+      <c r="H3" s="21" t="n"/>
+      <c r="I3" s="21" t="n"/>
     </row>
-    <row r="4" ht="14.5" customHeight="1" s="1">
+    <row r="4">
       <c r="A4" s="12" t="n"/>
       <c r="B4" s="12" t="n"/>
       <c r="C4" s="12" t="n"/>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_login_error_code</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t>登录错误码。成功为 0；失败取 NetResponse.ErrorCode；异常为 -1。</t>
         </is>
       </c>
-      <c r="G4" s="12" t="n"/>
-      <c r="H4" s="12" t="n"/>
-      <c r="I4" s="12" t="n"/>
+      <c r="G4" s="21" t="n"/>
+      <c r="H4" s="21" t="n"/>
+      <c r="I4" s="21" t="n"/>
     </row>
-    <row r="5" ht="14.5" customHeight="1" s="1">
+    <row r="5">
       <c r="A5" s="12" t="n"/>
       <c r="B5" s="12" t="n"/>
       <c r="C5" s="12" t="n"/>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_login_register_time</t>
         </is>
       </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F5" s="11" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>账号注册时间，秒级 Unix 时间戳；仅登录成功且响应有数据时上报。</t>
         </is>
       </c>
-      <c r="G5" s="12" t="n"/>
-      <c r="H5" s="12" t="n"/>
-      <c r="I5" s="12" t="n"/>
+      <c r="G5" s="21" t="n"/>
+      <c r="H5" s="21" t="n"/>
+      <c r="I5" s="21" t="n"/>
     </row>
-    <row r="6" ht="14.5" customHeight="1" s="1">
+    <row r="6">
       <c r="A6" s="12" t="n"/>
       <c r="B6" s="12" t="n"/>
       <c r="C6" s="12" t="n"/>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_login_time</t>
         </is>
       </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t>本次登录时间，秒级 Unix 时间戳；仅登录成功且响应有数据时上报。</t>
         </is>
       </c>
-      <c r="G6" s="12" t="n"/>
-      <c r="H6" s="12" t="n"/>
-      <c r="I6" s="12" t="n"/>
+      <c r="G6" s="21" t="n"/>
+      <c r="H6" s="21" t="n"/>
+      <c r="I6" s="21" t="n"/>
     </row>
-    <row r="7" ht="14.5" customHeight="1" s="1">
+    <row r="7">
       <c r="A7" s="12" t="n"/>
       <c r="B7" s="12" t="n"/>
       <c r="C7" s="12" t="n"/>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_login_is_new_account</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>是否为新注册账号；仅登录成功且响应有数据时上报。</t>
         </is>
       </c>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
     </row>
-    <row r="8" ht="14.5" customHeight="1" s="1">
+    <row r="8">
       <c r="A8" s="13" t="n"/>
       <c r="B8" s="13" t="n"/>
       <c r="C8" s="13" t="n"/>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_login_duration_ms</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t>登录调用耗时，单位毫秒，取非负整数。</t>
         </is>
       </c>
-      <c r="G8" s="13" t="n"/>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="13" t="n"/>
+      <c r="G8" s="21" t="n"/>
+      <c r="H8" s="21" t="n"/>
+      <c r="I8" s="21" t="n"/>
     </row>
-    <row r="9" ht="14.5" customHeight="1" s="1">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>nova_gamelogin_delete_account</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>删除账号完成</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>GameLogin 删除当前登录账号请求完成。成功、失败或异常均只上报一次。</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_delete_account_result</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>enum-string</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>删除结果。success=成功；failed=请求失败；exception=调用抛出异常。</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Login.DeleteAsync 请求取得最终结果时上报。</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>tga</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>删除成功时先上报本事件，再清空本地 UID 与 NetService 登录态。</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="14.5" customHeight="1" s="1">
+    <row r="10">
       <c r="A10" s="12" t="n"/>
       <c r="B10" s="12" t="n"/>
       <c r="C10" s="12" t="n"/>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_delete_account_error_code</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>删除账号错误码。成功为 0；失败取 NetResponse.ErrorCode；异常为 -1。</t>
         </is>
       </c>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
+      <c r="G10" s="21" t="n"/>
+      <c r="H10" s="21" t="n"/>
+      <c r="I10" s="21" t="n"/>
     </row>
-    <row r="11" ht="14.5" customHeight="1" s="1">
+    <row r="11">
       <c r="A11" s="13" t="n"/>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="13" t="n"/>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t>nova_gamelogin_delete_account_duration_ms</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>删除账号调用耗时，单位毫秒，取非负整数。</t>
         </is>
       </c>
-      <c r="G11" s="13" t="n"/>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="13" t="n"/>
+      <c r="G11" s="21" t="n"/>
+      <c r="H11" s="21" t="n"/>
+      <c r="I11" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="H9:H11"/>
-    <mergeCell ref="G9:G11"/>
+  <autoFilter ref="A1:I11"/>
+  <mergeCells count="6">
+    <mergeCell ref="C9:C11"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="B2:B8"/>
     <mergeCell ref="A2:A8"/>
-    <mergeCell ref="C9:C11"/>
     <mergeCell ref="C2:C8"/>
-    <mergeCell ref="G2:G8"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="H2:H8"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="I2:I8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
